--- a/mainWidget/mainWidget/src/database/计算模型-破片撞击试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-破片撞击试验.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E627C5B0-1896-4426-B6BD-CBC0348ED218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529E5662-C40C-46A7-9652-4EC00EEE16D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="1240">
   <si>
     <t>序号</t>
   </si>
@@ -308,1253 +308,3765 @@
   </si>
   <si>
     <t>-0.005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0042</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0075</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2124</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3465</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0479</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0926</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1148</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1495</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1872</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0159</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0313</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0579</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0792</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0177</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0222</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0269</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2535</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0868</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0078</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0438</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0285</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0542</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0697</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0469</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0971</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0053</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0848</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0035</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0093</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0039</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0041</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0033</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0264</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0267</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0265</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0037</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0081</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0253</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0151</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0054</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0036</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.035</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0033</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0142</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.7278</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9133</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0556</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0984</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8944</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.162</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.4652</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1239</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0071</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0216</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.489</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1972</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2287</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0069</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0794</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.4105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.671</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.7113</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>6.5535</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4.0598</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.7073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.6903</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0877</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0371</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1876</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.0385</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.9803</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0309</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0485</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1292</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.1037</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6716</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0776</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1651</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.2065</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0619</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0955</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0211</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0349</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0088</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0181</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0131</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0607</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0086</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0232</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0201</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3241</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1428</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0711</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4477</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3042</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0751</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0165</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0228</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0316</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0868</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1487</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1309</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0229</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0467</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0128</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0197</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2467</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0501</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2426</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0341</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1859</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.039</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0158</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0199</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1756</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.036</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0062</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0174</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1624</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5204</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9136</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0594</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0155</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.1022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.9582</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3842</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5152</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.3393</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.378</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.1106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4117</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0084</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0276</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0664</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9734</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2903</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0244</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.053</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.838</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7098</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.062</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.076</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0044</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0642</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.72</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0573</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0505</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0947</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0463</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0456</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7452</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0549</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.052</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7718</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.8329</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.181</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.1321</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.0378</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6092</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1982</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0312</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7679</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.621</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3936</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.483</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0334</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9369</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.9016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3546</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2197</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.771</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5332</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0403</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-7.8836</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-6.2533</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0981</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3096</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.7188</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.6753</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.5457</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.2058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4.587</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.6123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0543</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5673</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1174</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.3555</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0484</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-139.6736</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-150.6801</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>539.0658</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>970.3825</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>433.2151</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-80.7179</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.7761</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>31.3849</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>44.5054</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>643.6441</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-35.2369</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.4541</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>33.8077</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>37.2226</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>400.1964</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-79.0359</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.0667</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>26.1442</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>38.4823</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>398.9091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-24.2324</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7839</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>29.1597</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>24.5833</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>373.4908</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-28.0752</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2487</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>25.5071</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>43.9758</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>334.2641</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-25.196</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9817</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>37.8351</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>47.3898</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>322.665</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-59.1798</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-13.7867</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>326.4528</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>331.3298</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>202.0684</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>244.6160 + 0.0001*B + 0.0000*C + 0.0492*D + 0.0358*E - 0.0016*F + 0.0000*G + 0.6223*H + 0.0213*I + 0.0651*J - 0.5170*K + 0.4259*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>244.616</t>
+  </si>
+  <si>
+    <t>0.0001</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>0.0492</t>
+  </si>
+  <si>
+    <t>0.0358</t>
+  </si>
+  <si>
+    <t>-0.0016</t>
+  </si>
+  <si>
+    <t>0.6223</t>
+  </si>
+  <si>
+    <t>0.0213</t>
+  </si>
+  <si>
+    <t>0.0651</t>
+  </si>
+  <si>
+    <t>-0.517</t>
+  </si>
+  <si>
+    <t>0.4259</t>
+  </si>
+  <si>
+    <t>-0.0001</t>
+  </si>
+  <si>
+    <t>15.9012 + 0.0008*B + 0.0000*C - 0.2153*D - 0.0265*E - 0.0048*F + 0.0000*G - 0.5653*H + 0.0039*I - 0.1638*J - 0.9024*K + 2.8073*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>15.9012</t>
+  </si>
+  <si>
+    <t>0.0008</t>
+  </si>
+  <si>
+    <t>-0.2153</t>
+  </si>
+  <si>
+    <t>-0.0265</t>
+  </si>
+  <si>
+    <t>-0.0048</t>
+  </si>
+  <si>
+    <t>-0.5653</t>
+  </si>
+  <si>
+    <t>0.0039</t>
+  </si>
+  <si>
+    <t>-0.1638</t>
+  </si>
+  <si>
+    <t>-0.9024</t>
+  </si>
+  <si>
+    <t>2.8073</t>
+  </si>
+  <si>
+    <t>142.6244 - 0.0024*B + 0.0000*C - 0.0739*D + 0.0087*E - 0.0107*F + 0.0000*G + 1.5523*H - 0.0086*I - 0.0796*J - 0.5711*K + 3.8047*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>142.6244</t>
+  </si>
+  <si>
+    <t>-0.0024</t>
+  </si>
+  <si>
+    <t>-0.0739</t>
+  </si>
+  <si>
+    <t>0.0087</t>
+  </si>
+  <si>
+    <t>-0.0107</t>
+  </si>
+  <si>
+    <t>1.5523</t>
+  </si>
+  <si>
+    <t>-0.0086</t>
+  </si>
+  <si>
+    <t>-0.0796</t>
+  </si>
+  <si>
+    <t>-0.5711</t>
+  </si>
+  <si>
+    <t>3.8047</t>
+  </si>
+  <si>
+    <t>-0.0</t>
+  </si>
+  <si>
+    <t>-124.7771 + 0.0019*B + 0.0000*C - 0.1438*D + 0.0106*E - 0.0188*F + 0.0000*G - 1.0462*H + 0.0023*I + 0.0611*J - 0.2551*K - 1.2721*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-124.7771</t>
+  </si>
+  <si>
+    <t>0.0019</t>
+  </si>
+  <si>
+    <t>-0.1438</t>
+  </si>
+  <si>
+    <t>0.0106</t>
+  </si>
+  <si>
+    <t>-0.0188</t>
+  </si>
+  <si>
+    <t>-1.0462</t>
+  </si>
+  <si>
+    <t>0.0023</t>
+  </si>
+  <si>
+    <t>0.0611</t>
+  </si>
+  <si>
+    <t>-0.2551</t>
+  </si>
+  <si>
+    <t>-1.2721</t>
+  </si>
+  <si>
+    <t>-224.7785 - 0.0010*B + 0.0000*C - 0.0653*D + 0.0268*E + 0.0042*F + 0.0000*G - 1.7093*H + 0.0041*I - 0.0924*J - 0.6018*K + 0.6042*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-224.7785</t>
+  </si>
+  <si>
+    <t>-0.001</t>
+  </si>
+  <si>
+    <t>-0.0653</t>
+  </si>
+  <si>
+    <t>0.0268</t>
+  </si>
+  <si>
+    <t>0.0042</t>
+  </si>
+  <si>
+    <t>-1.7093</t>
+  </si>
+  <si>
+    <t>0.0041</t>
+  </si>
+  <si>
+    <t>-0.0924</t>
+  </si>
+  <si>
+    <t>-0.6018</t>
+  </si>
+  <si>
+    <t>0.6042</t>
+  </si>
+  <si>
+    <t>347.8862 - 0.0013*B + 0.0000*C - 0.0496*D + 0.0129*E + 0.0106*F + 0.0000*G + 0.2486*H - 0.0029*I - 0.1909*J - 0.8141*K + 1.1224*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>347.8862</t>
+  </si>
+  <si>
+    <t>-0.0013</t>
+  </si>
+  <si>
+    <t>-0.0496</t>
+  </si>
+  <si>
+    <t>0.0129</t>
+  </si>
+  <si>
+    <t>0.2486</t>
+  </si>
+  <si>
+    <t>-0.0029</t>
+  </si>
+  <si>
+    <t>-0.1909</t>
+  </si>
+  <si>
+    <t>-0.8141</t>
+  </si>
+  <si>
+    <t>1.1224</t>
+  </si>
+  <si>
+    <t>109.4646 + 0.0023*B + 0.0000*C + 0.0196*D - 0.0058*E + 0.0044*F + 0.0000*G + 3.3248*H - 0.0009*I + 0.1740*J - 1.3960*K + 1.1466*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>109.4646</t>
+  </si>
+  <si>
+    <t>0.0196</t>
+  </si>
+  <si>
+    <t>-0.0058</t>
+  </si>
+  <si>
+    <t>0.0044</t>
+  </si>
+  <si>
+    <t>3.3248</t>
+  </si>
+  <si>
+    <t>-0.0009</t>
+  </si>
+  <si>
+    <t>0.174</t>
+  </si>
+  <si>
+    <t>-1.396</t>
+  </si>
+  <si>
+    <t>1.1466</t>
+  </si>
+  <si>
+    <t>55.5210 + 0.0005*B + 0.0000*C - 0.2230*D + 0.0024*E + 0.0044*F + 0.0000*G + 3.2331*H - 0.0075*I - 0.1502*J - 0.5302*K + 1.3878*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>55.521</t>
+  </si>
+  <si>
+    <t>0.0005</t>
+  </si>
+  <si>
+    <t>-0.223</t>
+  </si>
+  <si>
+    <t>0.0024</t>
+  </si>
+  <si>
+    <t>3.2331</t>
+  </si>
+  <si>
+    <t>-0.0075</t>
+  </si>
+  <si>
+    <t>-0.1502</t>
+  </si>
+  <si>
+    <t>-0.5302</t>
+  </si>
+  <si>
+    <t>1.3878</t>
+  </si>
+  <si>
+    <t>0.6850 + 0.0013*B + 0.0000*C - 0.0077*D + 0.0251*E - 0.0062*F + 0.0000*G + 0.4796*H - 0.0058*I - 0.2397*J - 0.2041*K - 0.3003*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>0.685</t>
+  </si>
+  <si>
+    <t>0.0013</t>
+  </si>
+  <si>
+    <t>-0.0077</t>
+  </si>
+  <si>
+    <t>0.0251</t>
+  </si>
+  <si>
+    <t>-0.0062</t>
+  </si>
+  <si>
+    <t>0.4796</t>
+  </si>
+  <si>
+    <t>-0.2397</t>
+  </si>
+  <si>
+    <t>-0.2041</t>
+  </si>
+  <si>
+    <t>-0.3003</t>
+  </si>
+  <si>
+    <t>70.8298 - 0.0024*B + 0.0000*C - 0.0611*D + 0.0000*E - 0.0072*F + 0.0000*G + 0.7334*H + 0.0052*I + 0.2179*J - 0.2538*K - 0.3093*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>70.8298</t>
+  </si>
+  <si>
+    <t>-0.0611</t>
+  </si>
+  <si>
+    <t>-0.0072</t>
+  </si>
+  <si>
+    <t>0.7334</t>
+  </si>
+  <si>
+    <t>0.0052</t>
+  </si>
+  <si>
+    <t>0.2179</t>
+  </si>
+  <si>
+    <t>-0.2538</t>
+  </si>
+  <si>
+    <t>-0.3093</t>
+  </si>
+  <si>
+    <t>-329.3992 + 0.0003*B + 0.0000*C - 0.0115*D + 0.0538*E - 0.0011*F + 0.0000*G + 1.4392*H - 0.0009*I - 0.1994*J + 0.1420*K + 0.9661*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-329.3992</t>
+  </si>
+  <si>
+    <t>0.0003</t>
+  </si>
+  <si>
+    <t>-0.0115</t>
+  </si>
+  <si>
+    <t>0.0538</t>
+  </si>
+  <si>
+    <t>-0.0011</t>
+  </si>
+  <si>
+    <t>1.4392</t>
+  </si>
+  <si>
+    <t>-0.1994</t>
+  </si>
+  <si>
+    <t>0.142</t>
+  </si>
+  <si>
+    <t>0.9661</t>
+  </si>
+  <si>
+    <t>-89.5295 + 0.0031*B + 0.0000*C - 0.1625*D + 0.0178*E + 0.0227*F + 0.0000*G - 0.5313*H - 0.0082*I - 0.0262*J - 0.5309*K - 4.9741*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-89.5295</t>
+  </si>
+  <si>
+    <t>0.0031</t>
+  </si>
+  <si>
+    <t>-0.1625</t>
+  </si>
+  <si>
+    <t>0.0178</t>
+  </si>
+  <si>
+    <t>0.0227</t>
+  </si>
+  <si>
+    <t>-0.5313</t>
+  </si>
+  <si>
+    <t>-0.0082</t>
+  </si>
+  <si>
+    <t>-0.0262</t>
+  </si>
+  <si>
+    <t>-0.5309</t>
+  </si>
+  <si>
+    <t>-4.9741</t>
+  </si>
+  <si>
+    <t>-125.8685 + 0.0013*B + 0.0000*C - 0.1127*D + 0.0363*E - 0.0071*F + 0.0000*G + 0.4882*H + 0.0108*I - 0.2079*J - 0.2321*K + 2.3984*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-125.8685</t>
+  </si>
+  <si>
+    <t>-0.1127</t>
+  </si>
+  <si>
+    <t>0.0363</t>
+  </si>
+  <si>
+    <t>-0.0071</t>
+  </si>
+  <si>
+    <t>0.4882</t>
+  </si>
+  <si>
+    <t>0.0108</t>
+  </si>
+  <si>
+    <t>-0.2079</t>
+  </si>
+  <si>
+    <t>-0.2321</t>
+  </si>
+  <si>
+    <t>2.3984</t>
+  </si>
+  <si>
+    <t>170.4534 + 0.0009*B + 0.0000*C + 0.0630*D - 0.0171*E - 0.0124*F + 0.0000*G + 1.7753*H + 0.0037*I - 0.0056*J - 0.1835*K - 2.7281*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>170.4534</t>
+  </si>
+  <si>
+    <t>0.0009</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>-0.0171</t>
+  </si>
+  <si>
+    <t>-0.0124</t>
+  </si>
+  <si>
+    <t>1.7753</t>
+  </si>
+  <si>
+    <t>0.0037</t>
+  </si>
+  <si>
+    <t>-0.0056</t>
+  </si>
+  <si>
+    <t>-0.1835</t>
+  </si>
+  <si>
+    <t>-2.7281</t>
+  </si>
+  <si>
+    <t>196.2227 - 0.0010*B + 0.0000*C + 0.1750*D + 0.0157*E - 0.0111*F + 0.0000*G + 1.9806*H - 0.0138*I + 0.0677*J + 0.1485*K - 3.0909*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>196.2227</t>
+  </si>
+  <si>
+    <t>0.175</t>
+  </si>
+  <si>
+    <t>0.0157</t>
+  </si>
+  <si>
+    <t>-0.0111</t>
+  </si>
+  <si>
+    <t>1.9806</t>
+  </si>
+  <si>
+    <t>-0.0138</t>
+  </si>
+  <si>
+    <t>0.0677</t>
+  </si>
+  <si>
+    <t>0.1485</t>
+  </si>
+  <si>
+    <t>-3.0909</t>
+  </si>
+  <si>
+    <t>224.6702 + 0.0019*B + 0.0000*C + 0.1782*D + 0.0019*E - 0.0068*F + 0.0000*G - 0.3772*H - 0.0116*I - 0.0503*J - 0.1857*K - 0.2600*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>224.6702</t>
+  </si>
+  <si>
+    <t>0.1782</t>
+  </si>
+  <si>
+    <t>-0.0068</t>
+  </si>
+  <si>
+    <t>-0.3772</t>
+  </si>
+  <si>
+    <t>-0.0116</t>
+  </si>
+  <si>
+    <t>-0.0503</t>
+  </si>
+  <si>
+    <t>-0.1857</t>
+  </si>
+  <si>
+    <t>-0.26</t>
+  </si>
+  <si>
+    <t>129.6668 + 0.0032*B + 0.0000*C - 0.0450*D + 0.0587*E + 0.0071*F + 0.0000*G - 0.3278*H - 0.0151*I + 0.0261*J - 0.4165*K + 0.8682*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>129.6668</t>
+  </si>
+  <si>
+    <t>0.0032</t>
+  </si>
+  <si>
+    <t>-0.045</t>
+  </si>
+  <si>
+    <t>0.0587</t>
+  </si>
+  <si>
+    <t>0.0071</t>
+  </si>
+  <si>
+    <t>-0.3278</t>
+  </si>
+  <si>
+    <t>-0.0151</t>
+  </si>
+  <si>
+    <t>0.0261</t>
+  </si>
+  <si>
+    <t>-0.4165</t>
+  </si>
+  <si>
+    <t>0.8682</t>
+  </si>
+  <si>
+    <t>109.2700 - 0.0013*B + 0.0000*C - 0.1742*D - 0.0020*E + 0.0094*F + 0.0000*G + 1.3058*H - 0.0175*I - 0.0161*J - 0.1676*K - 3.2539*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>109.27</t>
+  </si>
+  <si>
+    <t>-0.1742</t>
+  </si>
+  <si>
+    <t>-0.002</t>
+  </si>
+  <si>
+    <t>0.0094</t>
+  </si>
+  <si>
+    <t>1.3058</t>
+  </si>
+  <si>
+    <t>-0.0175</t>
+  </si>
+  <si>
+    <t>-0.0161</t>
+  </si>
+  <si>
+    <t>-0.1676</t>
+  </si>
+  <si>
+    <t>-3.2539</t>
+  </si>
+  <si>
+    <t>140.4097 - 0.0019*B + 0.0000*C + 0.0193*D + 0.0173*E + 0.0116*F + 0.0000*G + 2.5864*H - 0.0193*I - 0.1679*J - 0.1146*K + 0.3517*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>140.4097</t>
+  </si>
+  <si>
+    <t>-0.0019</t>
+  </si>
+  <si>
+    <t>0.0193</t>
+  </si>
+  <si>
+    <t>0.0173</t>
+  </si>
+  <si>
+    <t>0.0116</t>
+  </si>
+  <si>
+    <t>2.5864</t>
+  </si>
+  <si>
+    <t>-0.0193</t>
+  </si>
+  <si>
+    <t>-0.1679</t>
+  </si>
+  <si>
+    <t>-0.1146</t>
+  </si>
+  <si>
+    <t>0.3517</t>
+  </si>
+  <si>
+    <t>1042.1390 + 0.0015*B + 0.0000*C + 0.0996*D + 0.0249*E + 0.0073*F + 0.0000*G + 0.4985*H + 0.0100*I - 0.1454*J - 0.4219*K - 2.2259*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>1042.139</t>
+  </si>
+  <si>
+    <t>0.0015</t>
+  </si>
+  <si>
+    <t>0.0996</t>
+  </si>
+  <si>
+    <t>0.0249</t>
+  </si>
+  <si>
+    <t>0.0073</t>
+  </si>
+  <si>
+    <t>0.4985</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>-0.1454</t>
+  </si>
+  <si>
+    <t>-0.4219</t>
+  </si>
+  <si>
+    <t>-2.2259</t>
+  </si>
+  <si>
+    <t>676.6318 - 0.0033*B + 0.0000*C + 0.0532*D - 0.0243*E - 0.0039*F + 0.0000*G + 2.6400*H + 0.0005*I - 0.1870*J - 0.6175*K + 0.7794*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>676.6318</t>
+  </si>
+  <si>
+    <t>-0.0033</t>
+  </si>
+  <si>
+    <t>0.0532</t>
+  </si>
+  <si>
+    <t>-0.0243</t>
+  </si>
+  <si>
+    <t>-0.0039</t>
+  </si>
+  <si>
+    <t>2.64</t>
+  </si>
+  <si>
+    <t>-0.187</t>
+  </si>
+  <si>
+    <t>-0.6175</t>
+  </si>
+  <si>
+    <t>0.7794</t>
+  </si>
+  <si>
+    <t>178.0162 + 0.0004*B + 0.0000*C - 0.0850*D + 0.0477*E + 0.0071*F + 0.0000*G - 2.1090*H + 0.0022*I - 0.1302*J + 0.0233*K - 3.0183*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>178.0162</t>
+  </si>
+  <si>
+    <t>0.0004</t>
+  </si>
+  <si>
+    <t>-0.085</t>
+  </si>
+  <si>
+    <t>0.0477</t>
+  </si>
+  <si>
+    <t>-2.109</t>
+  </si>
+  <si>
+    <t>0.0022</t>
+  </si>
+  <si>
+    <t>-0.1302</t>
+  </si>
+  <si>
+    <t>0.0233</t>
+  </si>
+  <si>
+    <t>-3.0183</t>
+  </si>
+  <si>
+    <t>246.5821 + 0.0020*B + 0.0000*C - 0.1417*D + 0.0002*E - 0.0040*F + 0.0000*G - 0.0170*H + 0.0239*I + 0.0155*J - 0.8405*K + 1.3941*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>246.5821</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>-0.1417</t>
+  </si>
+  <si>
+    <t>0.0002</t>
+  </si>
+  <si>
+    <t>-0.004</t>
+  </si>
+  <si>
+    <t>-0.017</t>
+  </si>
+  <si>
+    <t>0.0239</t>
+  </si>
+  <si>
+    <t>0.0155</t>
+  </si>
+  <si>
+    <t>-0.8405</t>
+  </si>
+  <si>
+    <t>1.3941</t>
+  </si>
+  <si>
+    <t>371.9318 - 0.0026*B + 0.0000*C - 0.0677*D + 0.0308*E - 0.0063*F + 0.0000*G + 1.6562*H + 0.0103*I - 0.1664*J - 0.3495*K - 9.3355*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>371.9318</t>
+  </si>
+  <si>
+    <t>-0.0026</t>
+  </si>
+  <si>
+    <t>-0.0677</t>
+  </si>
+  <si>
+    <t>0.0308</t>
+  </si>
+  <si>
+    <t>-0.0063</t>
+  </si>
+  <si>
+    <t>1.6562</t>
+  </si>
+  <si>
+    <t>0.0103</t>
+  </si>
+  <si>
+    <t>-0.1664</t>
+  </si>
+  <si>
+    <t>-0.3495</t>
+  </si>
+  <si>
+    <t>-9.3355</t>
+  </si>
+  <si>
+    <t>66.5568 - 0.0021*B + 0.0000*C + 0.1509*D - 0.0208*E - 0.0036*F + 0.0000*G + 1.1787*H + 0.0194*I - 0.2359*J + 0.1503*K - 0.9474*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>66.5568</t>
+  </si>
+  <si>
+    <t>-0.0021</t>
+  </si>
+  <si>
+    <t>0.1509</t>
+  </si>
+  <si>
+    <t>-0.0208</t>
+  </si>
+  <si>
+    <t>-0.0036</t>
+  </si>
+  <si>
+    <t>1.1787</t>
+  </si>
+  <si>
+    <t>0.0194</t>
+  </si>
+  <si>
+    <t>-0.2359</t>
+  </si>
+  <si>
+    <t>0.1503</t>
+  </si>
+  <si>
+    <t>-0.9474</t>
+  </si>
+  <si>
+    <t>236.3912 + 0.0007*B + 0.0000*C - 0.0797*D + 0.0079*E - 0.0031*F + 0.0000*G + 1.1524*H + 0.0087*I + 0.1769*J - 0.8311*K + 4.5290*L - 0.0002*M</t>
+  </si>
+  <si>
+    <t>236.3912</t>
+  </si>
+  <si>
+    <t>0.0007</t>
+  </si>
+  <si>
+    <t>-0.0797</t>
+  </si>
+  <si>
+    <t>0.0079</t>
+  </si>
+  <si>
+    <t>-0.0031</t>
+  </si>
+  <si>
+    <t>1.1524</t>
+  </si>
+  <si>
+    <t>0.1769</t>
+  </si>
+  <si>
+    <t>-0.8311</t>
+  </si>
+  <si>
+    <t>4.529</t>
+  </si>
+  <si>
+    <t>-0.0002</t>
+  </si>
+  <si>
+    <t>90.5069 + 0.0015*B + 0.0000*C + 0.0113*D - 0.0054*E - 0.0013*F + 0.0000*G + 0.2275*H - 0.0085*I + 0.0763*J - 0.1792*K - 2.7613*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>90.5069</t>
+  </si>
+  <si>
+    <t>0.0113</t>
+  </si>
+  <si>
+    <t>-0.0054</t>
+  </si>
+  <si>
+    <t>0.2275</t>
+  </si>
+  <si>
+    <t>-0.0085</t>
+  </si>
+  <si>
+    <t>0.0763</t>
+  </si>
+  <si>
+    <t>-0.1792</t>
+  </si>
+  <si>
+    <t>-2.7613</t>
+  </si>
+  <si>
+    <t>199.6036 + 0.0019*B + 0.0000*C + 0.0473*D - 0.0093*E - 0.0048*F + 0.0000*G + 2.1190*H + 0.0080*I - 0.0426*J - 0.2772*K + 2.3223*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>199.6036</t>
+  </si>
+  <si>
+    <t>0.0473</t>
+  </si>
+  <si>
+    <t>-0.0093</t>
+  </si>
+  <si>
+    <t>2.119</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>-0.0426</t>
+  </si>
+  <si>
+    <t>-0.2772</t>
+  </si>
+  <si>
+    <t>2.3223</t>
+  </si>
+  <si>
+    <t>256.5891 + -0.0000*B + 0.0000*C - 0.0402*D + 0.0276*E + 0.0091*F + 0.0000*G + 2.2199*H + 0.0176*I - 0.0369*J - 0.0464*K - 1.7742*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>256.5891</t>
+  </si>
+  <si>
+    <t>-0.0402</t>
+  </si>
+  <si>
+    <t>0.0276</t>
+  </si>
+  <si>
+    <t>0.0091</t>
+  </si>
+  <si>
+    <t>2.2199</t>
+  </si>
+  <si>
+    <t>0.0176</t>
+  </si>
+  <si>
+    <t>-0.0369</t>
+  </si>
+  <si>
+    <t>-0.0464</t>
+  </si>
+  <si>
+    <t>-1.7742</t>
+  </si>
+  <si>
+    <t>95.6499 + 0.0005*B + 0.0000*C + 0.0438*D - 0.0091*E + 0.0217*F + 0.0000*G - 0.5549*H - 0.0170*I + 0.1184*J - 0.0015*K + 0.6363*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>95.6499</t>
+  </si>
+  <si>
+    <t>0.0438</t>
+  </si>
+  <si>
+    <t>-0.0091</t>
+  </si>
+  <si>
+    <t>0.0217</t>
+  </si>
+  <si>
+    <t>-0.5549</t>
+  </si>
+  <si>
+    <t>0.1184</t>
+  </si>
+  <si>
+    <t>-0.0015</t>
+  </si>
+  <si>
+    <t>0.6363</t>
+  </si>
+  <si>
+    <t>123.6667 - 0.0014*B + 0.0000*C - 0.0099*D - 0.0064*E + 0.0106*F + 0.0000*G + 0.7551*H - 0.0117*I - 0.0837*J - 0.1563*K - 2.4280*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>123.6667</t>
+  </si>
+  <si>
+    <t>-0.0014</t>
+  </si>
+  <si>
+    <t>-0.0099</t>
+  </si>
+  <si>
+    <t>-0.0064</t>
+  </si>
+  <si>
+    <t>0.7551</t>
+  </si>
+  <si>
+    <t>-0.0117</t>
+  </si>
+  <si>
+    <t>-0.0837</t>
+  </si>
+  <si>
+    <t>-0.1563</t>
+  </si>
+  <si>
+    <t>-2.428</t>
+  </si>
+  <si>
+    <t>184.4868 + 0.0008*B + 0.0000*C - 0.0701*D - 0.0025*E + 0.0031*F + 0.0000*G - 1.2290*H - 0.0197*I - 0.1379*J - 0.4124*K - 0.1717*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>184.4868</t>
+  </si>
+  <si>
+    <t>-0.0701</t>
+  </si>
+  <si>
+    <t>-0.0025</t>
+  </si>
+  <si>
+    <t>-1.229</t>
+  </si>
+  <si>
+    <t>-0.0197</t>
+  </si>
+  <si>
+    <t>-0.1379</t>
+  </si>
+  <si>
+    <t>-0.4124</t>
+  </si>
+  <si>
+    <t>-0.1717</t>
+  </si>
+  <si>
+    <t>330.3910 + 0.0000*B + 0.0000*C - 0.0197*D - 0.0126*E + 0.0006*F + 0.0000*G + 0.5391*H + 0.0041*I - 0.1528*J - 0.1128*K + 2.9804*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>330.391</t>
+  </si>
+  <si>
+    <t>-0.0126</t>
+  </si>
+  <si>
+    <t>0.0006</t>
+  </si>
+  <si>
+    <t>0.5391</t>
+  </si>
+  <si>
+    <t>-0.1528</t>
+  </si>
+  <si>
+    <t>-0.1128</t>
+  </si>
+  <si>
+    <t>2.9804</t>
+  </si>
+  <si>
+    <t>222.0397 + 0.0017*B + 0.0000*C - 0.0591*D + 0.0109*E + 0.0009*F + 0.0000*G + 1.1283*H - 0.0110*I - 0.0364*J - 0.1216*K + 2.7699*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>222.0397</t>
+  </si>
+  <si>
+    <t>0.0017</t>
+  </si>
+  <si>
+    <t>-0.0591</t>
+  </si>
+  <si>
+    <t>0.0109</t>
+  </si>
+  <si>
+    <t>1.1283</t>
+  </si>
+  <si>
+    <t>-0.011</t>
+  </si>
+  <si>
+    <t>-0.0364</t>
+  </si>
+  <si>
+    <t>-0.1216</t>
+  </si>
+  <si>
+    <t>2.7699</t>
+  </si>
+  <si>
+    <t>638.2587 - 0.0011*B + 0.0000*C + 0.0724*D + 0.0101*E + 0.0227*F + 0.0000*G - 0.2533*H - 0.0119*I - 0.1217*J - 1.1933*K - 2.3301*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>638.2587</t>
+  </si>
+  <si>
+    <t>0.0724</t>
+  </si>
+  <si>
+    <t>0.0101</t>
+  </si>
+  <si>
+    <t>-0.2533</t>
+  </si>
+  <si>
+    <t>-0.0119</t>
+  </si>
+  <si>
+    <t>-0.1217</t>
+  </si>
+  <si>
+    <t>-1.1933</t>
+  </si>
+  <si>
+    <t>-2.3301</t>
+  </si>
+  <si>
+    <t>162.3166 + 0.0010*B + 0.0000*C + 0.1761*D + 0.0248*E - 0.0050*F + 0.0000*G - 0.3908*H + 0.0064*I - 0.2201*J + 0.4235*K + 2.0689*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>162.3166</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.1761</t>
+  </si>
+  <si>
+    <t>0.0248</t>
+  </si>
+  <si>
+    <t>-0.005</t>
+  </si>
+  <si>
+    <t>-0.3908</t>
+  </si>
+  <si>
+    <t>0.0064</t>
+  </si>
+  <si>
+    <t>-0.2201</t>
+  </si>
+  <si>
+    <t>0.4235</t>
+  </si>
+  <si>
+    <t>2.0689</t>
+  </si>
+  <si>
+    <t>-280.5317 + 0.0030*B + 0.0000*C - 0.0295*D + 0.0303*E - 0.0152*F + 0.0000*G + 0.0653*H - 0.0003*I - 0.0334*J - 0.5091*K + 0.6330*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-280.5317</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>-0.0295</t>
+  </si>
+  <si>
+    <t>0.0303</t>
+  </si>
+  <si>
+    <t>-0.0152</t>
+  </si>
+  <si>
+    <t>0.0653</t>
+  </si>
+  <si>
+    <t>-0.0003</t>
+  </si>
+  <si>
+    <t>-0.0334</t>
+  </si>
+  <si>
+    <t>-0.5091</t>
+  </si>
+  <si>
+    <t>0.633</t>
+  </si>
+  <si>
+    <t>92.7420 + 0.0006*B + 0.0000*C + 0.0354*D + 0.0202*E - 0.0105*F + 0.0000*G - 1.3602*H + 0.0172*I + 0.0056*J - 0.6311*K + 3.0279*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>92.742</t>
+  </si>
+  <si>
+    <t>0.0354</t>
+  </si>
+  <si>
+    <t>0.0202</t>
+  </si>
+  <si>
+    <t>-0.0105</t>
+  </si>
+  <si>
+    <t>-1.3602</t>
+  </si>
+  <si>
+    <t>0.0172</t>
+  </si>
+  <si>
+    <t>0.0056</t>
+  </si>
+  <si>
+    <t>-0.6311</t>
+  </si>
+  <si>
+    <t>3.0279</t>
+  </si>
+  <si>
+    <t>406.8249 + 0.0005*B + 0.0000*C + 0.1951*D + 0.0402*E - 0.0017*F + 0.0000*G + 2.4610*H + 0.0085*I + 0.1472*J - 0.7196*K + 0.7961*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>406.8249</t>
+  </si>
+  <si>
+    <t>0.1951</t>
+  </si>
+  <si>
+    <t>0.0402</t>
+  </si>
+  <si>
+    <t>-0.0017</t>
+  </si>
+  <si>
+    <t>2.461</t>
+  </si>
+  <si>
+    <t>0.0085</t>
+  </si>
+  <si>
+    <t>0.1472</t>
+  </si>
+  <si>
+    <t>-0.7196</t>
+  </si>
+  <si>
+    <t>0.7961</t>
+  </si>
+  <si>
+    <t>-291.3693 - 0.0019*B + 0.0000*C - 0.2283*D + 0.0014*E + 0.0080*F + 0.0000*G + 3.2704*H + 0.0006*I + 0.1827*J - 0.8893*K - 5.3681*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-291.3693</t>
+  </si>
+  <si>
+    <t>-0.2283</t>
+  </si>
+  <si>
+    <t>0.0014</t>
+  </si>
+  <si>
+    <t>3.2704</t>
+  </si>
+  <si>
+    <t>0.1827</t>
+  </si>
+  <si>
+    <t>-0.8893</t>
+  </si>
+  <si>
+    <t>-5.3681</t>
+  </si>
+  <si>
+    <t>217.8462 + 0.0003*B + 0.0000*C - 0.2312*D + 0.0049*E - 0.0123*F + 0.0000*G + 2.0006*H + 0.0047*I - 0.1682*J - 0.5352*K - 3.7063*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>217.8462</t>
+  </si>
+  <si>
+    <t>-0.2312</t>
+  </si>
+  <si>
+    <t>0.0049</t>
+  </si>
+  <si>
+    <t>-0.0123</t>
+  </si>
+  <si>
+    <t>2.0006</t>
+  </si>
+  <si>
+    <t>0.0047</t>
+  </si>
+  <si>
+    <t>-0.1682</t>
+  </si>
+  <si>
+    <t>-0.5352</t>
+  </si>
+  <si>
+    <t>-3.7063</t>
+  </si>
+  <si>
+    <t>353.5568 - 0.0016*B + 0.0000*C + 0.0344*D - 0.0036*E - 0.0071*F + 0.0000*G + 0.8161*H - 0.0146*I - 0.1154*J - 0.8148*K + 4.0948*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>353.5568</t>
+  </si>
+  <si>
+    <t>0.0344</t>
+  </si>
+  <si>
+    <t>0.8161</t>
+  </si>
+  <si>
+    <t>-0.0146</t>
+  </si>
+  <si>
+    <t>-0.1154</t>
+  </si>
+  <si>
+    <t>-0.8148</t>
+  </si>
+  <si>
+    <t>4.0948</t>
+  </si>
+  <si>
+    <t>-39.7055 + 0.0008*B + 0.0000*C - 0.0293*D + 0.0023*E + 0.0069*F + 0.0000*G + 2.1345*H - 0.0077*I - 0.1184*J - 0.4376*K - 6.9122*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-39.7055</t>
+  </si>
+  <si>
+    <t>-0.0293</t>
+  </si>
+  <si>
+    <t>0.0069</t>
+  </si>
+  <si>
+    <t>2.1345</t>
+  </si>
+  <si>
+    <t>-0.1184</t>
+  </si>
+  <si>
+    <t>-0.4376</t>
+  </si>
+  <si>
+    <t>-6.9122</t>
+  </si>
+  <si>
+    <t>451.4006 + 0.0035*B + 0.0000*C - 0.0434*D + 0.0176*E + 0.0039*F + 0.0000*G + 5.6746*H + 0.0150*I - 0.0573*J - 0.7157*K - 5.1180*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>451.4006</t>
+  </si>
+  <si>
+    <t>0.0035</t>
+  </si>
+  <si>
+    <t>-0.0434</t>
+  </si>
+  <si>
+    <t>5.6746</t>
+  </si>
+  <si>
+    <t>0.015</t>
+  </si>
+  <si>
+    <t>-0.0573</t>
+  </si>
+  <si>
+    <t>-0.7157</t>
+  </si>
+  <si>
+    <t>-5.118</t>
+  </si>
+  <si>
+    <t>-53.1619 - 0.0024*B + 0.0000*C - 0.0845*D - 0.0141*E + 0.0177*F + 0.0000*G + 2.3238*H - 0.0005*I + 0.1624*J - 0.2935*K - 3.1957*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-53.1619</t>
+  </si>
+  <si>
+    <t>-0.0845</t>
+  </si>
+  <si>
+    <t>-0.0141</t>
+  </si>
+  <si>
+    <t>0.0177</t>
+  </si>
+  <si>
+    <t>2.3238</t>
+  </si>
+  <si>
+    <t>-0.0005</t>
+  </si>
+  <si>
+    <t>0.1624</t>
+  </si>
+  <si>
+    <t>-0.2935</t>
+  </si>
+  <si>
+    <t>-3.1957</t>
+  </si>
+  <si>
+    <t>254.6435 - 0.0017*B + 0.0000*C - 0.0374*D - 0.0102*E - 0.0131*F + 0.0000*G + 2.3918*H + 0.0258*I - 0.2308*J - 0.0950*K - 2.6523*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>254.6435</t>
+  </si>
+  <si>
+    <t>-0.0374</t>
+  </si>
+  <si>
+    <t>-0.0102</t>
+  </si>
+  <si>
+    <t>-0.0131</t>
+  </si>
+  <si>
+    <t>2.3918</t>
+  </si>
+  <si>
+    <t>0.0258</t>
+  </si>
+  <si>
+    <t>-0.2308</t>
+  </si>
+  <si>
+    <t>-0.095</t>
+  </si>
+  <si>
+    <t>-2.6523</t>
+  </si>
+  <si>
+    <t>-14.1993 - 0.0013*B + 0.0000*C - 0.0127*D - 0.0093*E + 0.0035*F + 0.0000*G + 0.9027*H - 0.0037*I - 0.1638*J - 0.5609*K + 0.9750*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-14.1993</t>
+  </si>
+  <si>
+    <t>-0.0127</t>
+  </si>
+  <si>
+    <t>0.9027</t>
+  </si>
+  <si>
+    <t>-0.0037</t>
+  </si>
+  <si>
+    <t>-0.5609</t>
+  </si>
+  <si>
+    <t>0.975</t>
+  </si>
+  <si>
+    <t>-105.7289 + 0.0005*B + 0.0000*C + 0.0599*D - 0.0254*E + 0.0062*F + 0.0000*G - 0.0312*H + 0.0075*I - 0.1440*J - 1.0629*K - 5.1725*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-105.7289</t>
+  </si>
+  <si>
+    <t>0.0599</t>
+  </si>
+  <si>
+    <t>-0.0254</t>
+  </si>
+  <si>
+    <t>0.0062</t>
+  </si>
+  <si>
+    <t>-0.0312</t>
+  </si>
+  <si>
+    <t>0.0075</t>
+  </si>
+  <si>
+    <t>-0.144</t>
+  </si>
+  <si>
+    <t>-1.0629</t>
+  </si>
+  <si>
+    <t>-5.1725</t>
+  </si>
+  <si>
+    <t>188.2974 - 0.0014*B + 0.0000*C + 0.0483*D - 0.0253*E + 0.0001*F + 0.0000*G - 0.8675*H - 0.0093*I - 0.0333*J - 0.6768*K - 1.9658*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>188.2974</t>
+  </si>
+  <si>
+    <t>0.0483</t>
+  </si>
+  <si>
+    <t>-0.0253</t>
+  </si>
+  <si>
+    <t>-0.8675</t>
+  </si>
+  <si>
+    <t>-0.0333</t>
+  </si>
+  <si>
+    <t>-0.6768</t>
+  </si>
+  <si>
+    <t>-1.9658</t>
+  </si>
+  <si>
+    <t>-10.5154 + 0.0020*B + 0.0000*C - 0.1344*D + 0.0167*E + 0.0152*F + 0.0000*G - 2.7900*H - 0.0113*I + 0.0390*J - 0.4081*K - 0.0163*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-10.5154</t>
+  </si>
+  <si>
+    <t>-0.1344</t>
+  </si>
+  <si>
+    <t>0.0167</t>
+  </si>
+  <si>
+    <t>0.0152</t>
+  </si>
+  <si>
+    <t>-2.79</t>
+  </si>
+  <si>
+    <t>-0.0113</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>-0.4081</t>
+  </si>
+  <si>
+    <t>-0.0163</t>
+  </si>
+  <si>
+    <t>147.1542 + 0.0000*B + 0.0000*C + 0.1029*D + 0.0114*E + 0.0042*F + 0.0000*G + 0.3512*H - 0.0071*I - 0.0989*J - 0.1639*K - 2.0598*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>147.1542</t>
+  </si>
+  <si>
+    <t>0.1029</t>
+  </si>
+  <si>
+    <t>0.0114</t>
+  </si>
+  <si>
+    <t>0.3512</t>
+  </si>
+  <si>
+    <t>-0.0989</t>
+  </si>
+  <si>
+    <t>-0.1639</t>
+  </si>
+  <si>
+    <t>-2.0598</t>
+  </si>
+  <si>
+    <t>619.7747 + 0.0020*B + 0.0000*C - 0.0514*D + 0.0296*E - 0.0033*F + 0.0000*G - 2.1288*H - 0.0142*I - 0.2953*J - 0.4688*K - 0.9262*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>619.7747</t>
+  </si>
+  <si>
+    <t>-0.0514</t>
+  </si>
+  <si>
+    <t>0.0296</t>
+  </si>
+  <si>
+    <t>-2.1288</t>
+  </si>
+  <si>
+    <t>-0.0142</t>
+  </si>
+  <si>
+    <t>-0.2953</t>
+  </si>
+  <si>
+    <t>-0.4688</t>
+  </si>
+  <si>
+    <t>-0.9262</t>
+  </si>
+  <si>
+    <t>204.2680 - 0.0001*B + 0.0000*C + 0.0680*D - 0.0358*E + 0.0031*F + 0.0000*G + 2.1549*H - 0.0207*I + 0.1165*J - 0.1868*K - 2.0451*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>204.268</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>-0.0358</t>
+  </si>
+  <si>
+    <t>2.1549</t>
+  </si>
+  <si>
+    <t>-0.0207</t>
+  </si>
+  <si>
+    <t>0.1165</t>
+  </si>
+  <si>
+    <t>-0.1868</t>
+  </si>
+  <si>
+    <t>-2.0451</t>
+  </si>
+  <si>
+    <t>666.1838 + 0.0007*B + 0.0000*C + 0.0079*D - 0.0022*E - 0.0077*F + 0.0000*G + 2.2456*H - 0.0121*I - 0.0300*J - 0.5204*K + 0.2619*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>666.1838</t>
+  </si>
+  <si>
+    <t>-0.0022</t>
+  </si>
+  <si>
+    <t>2.2456</t>
+  </si>
+  <si>
+    <t>-0.0121</t>
+  </si>
+  <si>
+    <t>-0.03</t>
+  </si>
+  <si>
+    <t>-0.5204</t>
+  </si>
+  <si>
+    <t>0.2619</t>
+  </si>
+  <si>
+    <t>373.1377 - 0.0006*B + 0.0000*C - 0.0456*D - 0.0122*E - 0.0037*F + 0.0000*G + 1.5547*H + 0.0100*I - 0.1658*J + 0.0303*K + 2.5235*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>373.1377</t>
+  </si>
+  <si>
+    <t>-0.0006</t>
+  </si>
+  <si>
+    <t>-0.0456</t>
+  </si>
+  <si>
+    <t>-0.0122</t>
+  </si>
+  <si>
+    <t>1.5547</t>
+  </si>
+  <si>
+    <t>-0.1658</t>
+  </si>
+  <si>
+    <t>2.5235</t>
+  </si>
+  <si>
+    <t>572.5782 - 0.0011*B + 0.0000*C - 0.1463*D - 0.0275*E + 0.0158*F + 0.0000*G + 1.9772*H - 0.0011*I - 0.0015*J - 0.7852*K + 5.3357*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>572.5782</t>
+  </si>
+  <si>
+    <t>-0.1463</t>
+  </si>
+  <si>
+    <t>-0.0275</t>
+  </si>
+  <si>
+    <t>0.0158</t>
+  </si>
+  <si>
+    <t>1.9772</t>
+  </si>
+  <si>
+    <t>-0.7852</t>
+  </si>
+  <si>
+    <t>5.3357</t>
+  </si>
+  <si>
+    <t>152.5736 + 0.0017*B + 0.0000*C + 0.0320*D + 0.0109*E - 0.0071*F + 0.0000*G + 1.6983*H + 0.0255*I + 0.1440*J + 0.3261*K - 2.2926*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>152.5736</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>1.6983</t>
+  </si>
+  <si>
+    <t>0.0255</t>
+  </si>
+  <si>
+    <t>0.144</t>
+  </si>
+  <si>
+    <t>0.3261</t>
+  </si>
+  <si>
+    <t>-2.2926</t>
+  </si>
+  <si>
+    <t>96.6851 + 0.0005*B + 0.0000*C + 0.0953*D - 0.0259*E + 0.0161*F + 0.0000*G + 0.7384*H - 0.0062*I - 0.1780*J - 1.0016*K + 1.1498*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>96.6851</t>
+  </si>
+  <si>
+    <t>0.0953</t>
+  </si>
+  <si>
+    <t>-0.0259</t>
+  </si>
+  <si>
+    <t>0.0161</t>
+  </si>
+  <si>
+    <t>0.7384</t>
+  </si>
+  <si>
+    <t>-0.178</t>
+  </si>
+  <si>
+    <t>-1.0016</t>
+  </si>
+  <si>
+    <t>1.1498</t>
+  </si>
+  <si>
+    <t>-179.9689 - 0.0021*B + 0.0000*C - 0.0524*D + 0.0386*E - 0.0018*F + 0.0000*G - 1.3130*H - 0.0037*I - 0.0770*J - 1.4275*K - 1.1138*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-179.9689</t>
+  </si>
+  <si>
+    <t>-0.0524</t>
+  </si>
+  <si>
+    <t>0.0386</t>
+  </si>
+  <si>
+    <t>-0.0018</t>
+  </si>
+  <si>
+    <t>-1.313</t>
+  </si>
+  <si>
+    <t>-0.077</t>
+  </si>
+  <si>
+    <t>-1.4275</t>
+  </si>
+  <si>
+    <t>-1.1138</t>
+  </si>
+  <si>
+    <t>292.0233 + 0.0039*B + 0.0000*C + 0.0987*D + 0.0014*E - 0.0103*F + 0.0000*G + 4.9037*H + 0.0004*I - 0.0379*J - 0.3350*K - 0.4628*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>292.0233</t>
+  </si>
+  <si>
+    <t>0.0987</t>
+  </si>
+  <si>
+    <t>-0.0103</t>
+  </si>
+  <si>
+    <t>4.9037</t>
+  </si>
+  <si>
+    <t>-0.0379</t>
+  </si>
+  <si>
+    <t>-0.335</t>
+  </si>
+  <si>
+    <t>-0.4628</t>
+  </si>
+  <si>
+    <t>-9.7478 - 0.0007*B + 0.0000*C - 0.0211*D - 0.0038*E - 0.0063*F + 0.0000*G + 1.1416*H - 0.0039*I + 0.1657*J - 1.4088*K + 1.8421*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-9.7478</t>
+  </si>
+  <si>
+    <t>-0.0007</t>
+  </si>
+  <si>
+    <t>-0.0211</t>
+  </si>
+  <si>
+    <t>-0.0038</t>
+  </si>
+  <si>
+    <t>1.1416</t>
+  </si>
+  <si>
+    <t>0.1657</t>
+  </si>
+  <si>
+    <t>-1.4088</t>
+  </si>
+  <si>
+    <t>1.8421</t>
+  </si>
+  <si>
+    <t>-366.1428 - 0.0003*B + 0.0000*C - 0.0561*D - 0.0204*E - 0.0070*F + 0.0000*G - 0.7143*H + 0.0237*I + 0.0880*J + 0.1947*K + 0.8880*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-366.1428</t>
+  </si>
+  <si>
+    <t>-0.0561</t>
+  </si>
+  <si>
+    <t>-0.0204</t>
+  </si>
+  <si>
+    <t>-0.007</t>
+  </si>
+  <si>
+    <t>-0.7143</t>
+  </si>
+  <si>
+    <t>0.0237</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>0.1947</t>
+  </si>
+  <si>
+    <t>0.888</t>
+  </si>
+  <si>
+    <t>1.9302 + 0.0013*B + 0.0000*C - 0.1439*D + 0.0202*E - 0.0016*F + 0.0000*G + 0.4077*H + 0.0094*I + 0.0209*J - 0.4727*K + 2.0170*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>1.9302</t>
+  </si>
+  <si>
+    <t>-0.1439</t>
+  </si>
+  <si>
+    <t>0.4077</t>
+  </si>
+  <si>
+    <t>0.0209</t>
+  </si>
+  <si>
+    <t>-0.4727</t>
+  </si>
+  <si>
+    <t>2.017</t>
+  </si>
+  <si>
+    <t>272.9478 + 0.0015*B + 0.0000*C - 0.0497*D + 0.0128*E - 0.0117*F + 0.0000*G + 2.3885*H - 0.0029*I - 0.1112*J + 0.1037*K - 2.7908*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>272.9478</t>
+  </si>
+  <si>
+    <t>-0.0497</t>
+  </si>
+  <si>
+    <t>0.0128</t>
+  </si>
+  <si>
+    <t>2.3885</t>
+  </si>
+  <si>
+    <t>-0.1112</t>
+  </si>
+  <si>
+    <t>0.1037</t>
+  </si>
+  <si>
+    <t>-2.7908</t>
+  </si>
+  <si>
+    <t>-243.3398 + 0.0015*B + 0.0000*C - 0.1500*D + 0.0402*E - 0.0201*F + 0.0000*G + 3.5664*H + 0.0025*I - 0.0530*J - 0.5479*K + 0.0559*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-243.3398</t>
+  </si>
+  <si>
+    <t>-0.15</t>
+  </si>
+  <si>
+    <t>-0.0201</t>
+  </si>
+  <si>
+    <t>3.5664</t>
+  </si>
+  <si>
+    <t>0.0025</t>
+  </si>
+  <si>
+    <t>-0.053</t>
+  </si>
+  <si>
+    <t>-0.5479</t>
+  </si>
+  <si>
+    <t>0.0559</t>
+  </si>
+  <si>
+    <t>388.7654 + 0.0006*B + 0.0000*C - 0.0022*D - 0.0004*E + 0.0002*F + 0.0000*G + 1.4487*H - 0.0239*I - 0.2239*J - 0.0213*K - 0.5330*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>388.7654</t>
+  </si>
+  <si>
+    <t>-0.0004</t>
+  </si>
+  <si>
+    <t>1.4487</t>
+  </si>
+  <si>
+    <t>-0.0239</t>
+  </si>
+  <si>
+    <t>-0.2239</t>
+  </si>
+  <si>
+    <t>-0.0213</t>
+  </si>
+  <si>
+    <t>-0.533</t>
+  </si>
+  <si>
+    <t>130.9577 + 0.0010*B + 0.0000*C - 0.0735*D - 0.0083*E + 0.0028*F + 0.0000*G - 0.5127*H + 0.0052*I - 0.2724*J + 0.0956*K + 0.2454*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>130.9577</t>
+  </si>
+  <si>
+    <t>-0.0735</t>
+  </si>
+  <si>
+    <t>-0.0083</t>
+  </si>
+  <si>
+    <t>0.0028</t>
+  </si>
+  <si>
+    <t>-0.5127</t>
+  </si>
+  <si>
+    <t>-0.2724</t>
+  </si>
+  <si>
+    <t>0.0956</t>
+  </si>
+  <si>
+    <t>0.2454</t>
+  </si>
+  <si>
+    <t>360.1034 + 0.0036*B + 0.0000*C + 0.0871*D - 0.0287*E - 0.0120*F + 0.0000*G + 0.0265*H + -0.0000*I + 0.0309*J - 0.6218*K - 0.4919*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>360.1034</t>
+  </si>
+  <si>
+    <t>0.0036</t>
+  </si>
+  <si>
+    <t>0.0871</t>
+  </si>
+  <si>
+    <t>-0.0287</t>
+  </si>
+  <si>
+    <t>-0.012</t>
+  </si>
+  <si>
+    <t>0.0265</t>
+  </si>
+  <si>
+    <t>0.0309</t>
+  </si>
+  <si>
+    <t>-0.6218</t>
+  </si>
+  <si>
+    <t>-0.4919</t>
+  </si>
+  <si>
+    <t>-18.7439 - 0.0024*B + 0.0000*C - 0.1131*D - 0.0193*E - 0.0090*F + 0.0000*G + 2.5861*H - 0.0134*I + 0.3198*J - 0.1235*K - 0.4969*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-18.7439</t>
+  </si>
+  <si>
+    <t>-0.1131</t>
+  </si>
+  <si>
+    <t>-0.009</t>
+  </si>
+  <si>
+    <t>2.5861</t>
+  </si>
+  <si>
+    <t>-0.0134</t>
+  </si>
+  <si>
+    <t>0.3198</t>
+  </si>
+  <si>
+    <t>-0.1235</t>
+  </si>
+  <si>
+    <t>-0.4969</t>
+  </si>
+  <si>
+    <t>292.9985 - 0.0008*B + 0.0000*C - 0.0051*D + 0.0556*E - 0.0002*F + 0.0000*G + 2.7320*H - 0.0100*I - 0.0446*J + 0.3987*K - 2.5912*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>292.9985</t>
+  </si>
+  <si>
+    <t>-0.0008</t>
+  </si>
+  <si>
+    <t>-0.0051</t>
+  </si>
+  <si>
+    <t>0.0556</t>
+  </si>
+  <si>
+    <t>2.732</t>
+  </si>
+  <si>
+    <t>-0.01</t>
+  </si>
+  <si>
+    <t>-0.0446</t>
+  </si>
+  <si>
+    <t>0.3987</t>
+  </si>
+  <si>
+    <t>-2.5912</t>
+  </si>
+  <si>
+    <t>294.7670 - 0.0007*B + 0.0000*C + 0.0476*D + 0.0252*E + 0.0070*F + 0.0000*G - 1.4153*H - 0.0104*I - 0.0736*J - 0.3556*K + 0.6274*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>294.767</t>
+  </si>
+  <si>
+    <t>0.0476</t>
+  </si>
+  <si>
+    <t>0.0252</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
+    <t>-1.4153</t>
+  </si>
+  <si>
+    <t>-0.0104</t>
+  </si>
+  <si>
+    <t>-0.0736</t>
+  </si>
+  <si>
+    <t>-0.3556</t>
+  </si>
+  <si>
+    <t>0.6274</t>
+  </si>
+  <si>
+    <t>-190.7538 + 0.0011*B + 0.0000*C + 0.0454*D + 0.0173*E + 0.0116*F + 0.0000*G + 2.2511*H + 0.0059*I - 0.0494*J - 1.0041*K + 0.1346*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-190.7538</t>
+  </si>
+  <si>
+    <t>0.0011</t>
+  </si>
+  <si>
+    <t>0.0454</t>
+  </si>
+  <si>
+    <t>2.2511</t>
+  </si>
+  <si>
+    <t>0.0059</t>
+  </si>
+  <si>
+    <t>-0.0494</t>
+  </si>
+  <si>
+    <t>-1.0041</t>
+  </si>
+  <si>
+    <t>0.1346</t>
+  </si>
+  <si>
+    <t>191.1150 - 0.0021*B + 0.0000*C - 0.1294*D + 0.0268*E + 0.0004*F + 0.0000*G + 2.0186*H + 0.0000*I - 0.0357*J + 0.0584*K - 2.3050*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>191.115</t>
+  </si>
+  <si>
+    <t>-0.1294</t>
+  </si>
+  <si>
+    <t>2.0186</t>
+  </si>
+  <si>
+    <t>-0.0357</t>
+  </si>
+  <si>
+    <t>0.0584</t>
+  </si>
+  <si>
+    <t>-2.305</t>
+  </si>
+  <si>
+    <t>16.7221 - 0.0005*B + 0.0000*C - 0.0496*D + 0.0108*E - 0.0040*F + 0.0000*G + 2.8944*H - 0.0127*I - 0.0653*J - 0.5049*K + 2.7591*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>16.7221</t>
+  </si>
+  <si>
+    <t>2.8944</t>
+  </si>
+  <si>
+    <t>-0.5049</t>
+  </si>
+  <si>
+    <t>2.7591</t>
+  </si>
+  <si>
+    <t>371.7843 - 0.0025*B + 0.0000*C + 0.0099*D + 0.0236*E + 0.0016*F + 0.0000*G + 2.6042*H - 0.0075*I + 0.1527*J + 0.6146*K - 1.9098*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>371.7843</t>
+  </si>
+  <si>
+    <t>0.0099</t>
+  </si>
+  <si>
+    <t>0.0236</t>
+  </si>
+  <si>
+    <t>0.0016</t>
+  </si>
+  <si>
+    <t>2.6042</t>
+  </si>
+  <si>
+    <t>0.1527</t>
+  </si>
+  <si>
+    <t>0.6146</t>
+  </si>
+  <si>
+    <t>-1.9098</t>
+  </si>
+  <si>
+    <t>471.9589 + 0.0034*B + 0.0000*C - 0.0717*D - 0.0015*E - 0.0020*F + 0.0000*G - 1.0710*H - 0.0130*I - 0.1770*J - 0.6390*K - 1.0632*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>471.9589</t>
+  </si>
+  <si>
+    <t>0.0034</t>
+  </si>
+  <si>
+    <t>-0.0717</t>
+  </si>
+  <si>
+    <t>-1.071</t>
+  </si>
+  <si>
+    <t>-0.013</t>
+  </si>
+  <si>
+    <t>-0.177</t>
+  </si>
+  <si>
+    <t>-0.639</t>
+  </si>
+  <si>
+    <t>-1.0632</t>
+  </si>
+  <si>
+    <t>495.0375 - 0.0016*B + 0.0000*C + 0.0840*D + 0.0025*E + 0.0003*F + 0.0000*G + 2.0084*H - 0.0158*I + 0.0125*J - 0.2571*K + 0.2966*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>495.0375</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>2.0084</t>
+  </si>
+  <si>
+    <t>-0.0158</t>
+  </si>
+  <si>
+    <t>0.0125</t>
+  </si>
+  <si>
+    <t>-0.2571</t>
+  </si>
+  <si>
+    <t>0.2966</t>
+  </si>
+  <si>
+    <t>710.0538 - 0.0009*B + 0.0000*C - 0.0725*D - 0.0054*E - 0.0048*F + 0.0000*G + 0.0073*H + 0.0160*I + 0.1543*J - 0.5584*K - 3.1211*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>710.0538</t>
+  </si>
+  <si>
+    <t>-0.0725</t>
+  </si>
+  <si>
+    <t>0.016</t>
+  </si>
+  <si>
+    <t>0.1543</t>
+  </si>
+  <si>
+    <t>-0.5584</t>
+  </si>
+  <si>
+    <t>-3.1211</t>
+  </si>
+  <si>
+    <t>-4.6531 + 0.0016*B + 0.0000*C + 0.0033*D - 0.0225*E + 0.0163*F + 0.0000*G + 3.7180*H - 0.0088*I - 0.0927*J - 0.2083*K - 0.1109*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-4.6531</t>
+  </si>
+  <si>
+    <t>0.0033</t>
+  </si>
+  <si>
+    <t>-0.0225</t>
+  </si>
+  <si>
+    <t>0.0163</t>
+  </si>
+  <si>
+    <t>3.718</t>
+  </si>
+  <si>
+    <t>-0.0088</t>
+  </si>
+  <si>
+    <t>-0.0927</t>
+  </si>
+  <si>
+    <t>-0.2083</t>
+  </si>
+  <si>
+    <t>-0.1109</t>
+  </si>
+  <si>
+    <t>604.2814 + 0.0000*B + 0.0000*C - 0.1002*D - 0.0199*E - 0.0065*F + 0.0000*G + 0.9288*H + 0.0243*I - 0.1105*J - 0.2336*K - 1.0161*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>604.2814</t>
+  </si>
+  <si>
+    <t>-0.1002</t>
+  </si>
+  <si>
+    <t>-0.0199</t>
+  </si>
+  <si>
+    <t>-0.0065</t>
+  </si>
+  <si>
+    <t>0.9288</t>
+  </si>
+  <si>
+    <t>0.0243</t>
+  </si>
+  <si>
+    <t>-0.1105</t>
+  </si>
+  <si>
+    <t>-0.2336</t>
+  </si>
+  <si>
+    <t>-1.0161</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1566,6 +4078,10 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1585,21 +4101,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="text_style" xfId="2" xr:uid="{222C8633-44F2-4636-A207-233C838BCF00}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{2CE74D15-27A4-4457-98C6-BECE98FAFA34}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1901,7 +4426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="9.23046875" style="1"/>
@@ -3836,8 +6361,3768 @@
         <v>107</v>
       </c>
     </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="I53" s="2">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="O62" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="I63" s="2">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="O66" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="O67" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="N68" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="O72" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="M80" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="M82" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="N82" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="N84" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="N85" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="O86" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="N87" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="O87" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="N89" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="I90" s="2">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="I91" s="2">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="L91" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="M91" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="N91" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="O91" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="M94" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="N95" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="I96" s="2">
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="M96" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="N96" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="I97" s="2">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="N97" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="O98" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="N99" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="I100" s="2">
+        <v>0</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="L100" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="N100" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="O100" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="N101" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="L102" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="M102" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="N102" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="M103" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="N103" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="O103" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="M104" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="N104" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="O104" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="N105" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="O105" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="M106" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="N106" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M107" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="N107" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="O107" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="L108" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="M108" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="N108" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="L109" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M109" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="N109" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="O109" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="L110" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M110" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="N110" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="O110" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L111" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M111" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N111" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O111" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="M112" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="N112" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="M113" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="N113" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="E114" s="2">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="L114" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="M114" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="N114" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="E115" s="2">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="L115" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="M115" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="N115" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="O115" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="L116" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="M116" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="N116" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O116" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L117" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="N117" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="O117" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K118" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L118" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="M118" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="N118" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="K119" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L119" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="N119" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="O119" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L120" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="M120" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="N120" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L121" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="N121" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="O121" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>